--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Planificación Inicial/Matriz de Riesgos - TTDH Automation.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Planificación Inicial/Matriz de Riesgos - TTDH Automation.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Exposición de datos sensibles de deudores (RUT, montos y cuentas) al enviar documentos a un servicio externo de OCR/IA en la nube.</t>
+          <t>Exposición de datos sensibles de deudores (RUT, montos y cuentas) durante la extracción y el almacenamiento de los documentos.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Medio</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Usar solo documentos simulados durante el proyecto. En producción: anonimizar o enmascarar los datos antes del envío, contratar un servicio sin retención de datos o usar OCR local, y registrar cada envío en la bitácora.</t>
+          <t>Extracción con Tesseract OCR ejecutado localmente, sin envío de documentos a servicios externos; uso exclusivo de documentos simulados durante el proyecto; cifrado de la base de datos (AES-256) y registro de cada acceso en la bitácora.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
